--- a/SGI_Sistema-de-gestao-integrado/SGI_Sistema-de-gestao-da-qualidade/Registos_SGQ_Plasticom/SGQ-00_Indice_Modelo_Dados.xlsx
+++ b/SGI_Sistema-de-gestao-integrado/SGI_Sistema-de-gestao-da-qualidade/Registos_SGQ_Plasticom/SGQ-00_Indice_Modelo_Dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project Portfolios\manufacturing-performance-analytics\SGI_Sistema-de-gestao-integrado\SGI_Sistema-de-gestao-da-qualidade\Registos_SGQ_Plasticom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10297A16-3677-418A-99A1-EE9A5D38545E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13D0164D-73A8-4BD7-B9D4-085907281E51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4529,7 +4529,7 @@
     <t>Injeção de tampas e potes</t>
   </si>
   <si>
-    <t>IM-001 a IM-008</t>
+    <t>IM-001 a IM-009</t>
   </si>
   <si>
     <t>SOP</t>
